--- a/docs/nuclear-literature-database.xlsx
+++ b/docs/nuclear-literature-database.xlsx
@@ -38742,7 +38742,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-23T10:21:04</t>
+          <t>2026-09-23T10:25:49</t>
         </is>
       </c>
       <c r="E2" t="n">
